--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-11-2025.xlsx
@@ -563,12 +563,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£9.73</t>
+          <t>£9.69</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£9.79</t>
+          <t>£9.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -803,7 +803,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£14.10</t>
+          <t>£14.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -923,12 +923,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£14.59</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£14.70</t>
+          <t>£14.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£18.20</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£20.49</t>
+          <t>£20.30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£20.38</t>
+          <t>£20.30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£23.44</t>
+          <t>£23.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£23.63</t>
+          <t>£23.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£25.48</t>
+          <t>£25.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£25.68</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£25.14</t>
+          <t>£25.10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£32.19</t>
+          <t>£32.15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£30.49</t>
+          <t>£30.45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£37.73</t>
+          <t>£37.40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£38.99</t>
+          <t>£38.50</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£37.67</t>
+          <t>£37.50</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£41.30</t>
+          <t>£40.48</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>£81.9</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff63b7ca235
-	0x7ff63b522630
-	0x7ff63b2b16dd
-	0x7ff63b30a27e
-	0x7ff63b30a58c
-	0x7ff63b35ed77
-	0x7ff63b35baba
-	0x7ff63b2fb0ed
-	0x7ff63b2fbf63
-	0x7ff63b7f5d60
-	0x7ff63b7efe8a
-	0x7ff63b811005
-	0x7ff63b53d71e
-	0x7ff63b544e1f
-	0x7ff63b52b7c4
-	0x7ff63b52b97f
-	0x7ff63b5118e8
+	0x7ff6c361a235
+	0x7ff6c3372630
+	0x7ff6c31016dd
+	0x7ff6c315a27e
+	0x7ff6c315a58c
+	0x7ff6c31aed77
+	0x7ff6c31ababa
+	0x7ff6c314b0ed
+	0x7ff6c314bf63
+	0x7ff6c3645d60
+	0x7ff6c363fe8a
+	0x7ff6c3661005
+	0x7ff6c338d71e
+	0x7ff6c3394e1f
+	0x7ff6c337b7c4
+	0x7ff6c337b97f
+	0x7ff6c33618e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
